--- a/docs/downloads/05/tbl_water_alaotra_ambodivoara.xlsx
+++ b/docs/downloads/05/tbl_water_alaotra_ambodivoara.xlsx
@@ -387,12 +387,6 @@
           <t>Autre ____________________________</t>
         </is>
       </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>6.9</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -561,12 +555,6 @@
         <is>
           <t>Alaotra - Tous</t>
         </is>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>0.2</v>
       </c>
     </row>
   </sheetData>
